--- a/server/xlsx/道具表.xlsx
+++ b/server/xlsx/道具表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27045" windowHeight="12060" firstSheet="3"/>
+    <workbookView windowWidth="23310" windowHeight="12315" firstSheet="3"/>
   </bookViews>
   <sheets>
     <sheet name="道具表" sheetId="5" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
   <si>
     <t>id</t>
   </si>
@@ -38,19 +38,43 @@
     <t>怪物名称</t>
   </si>
   <si>
+    <t>出售价格</t>
+  </si>
+  <si>
     <t>icon</t>
   </si>
   <si>
     <t>desc</t>
   </si>
   <si>
+    <t>value</t>
+  </si>
+  <si>
     <t>String</t>
   </si>
   <si>
+    <t>Num</t>
+  </si>
+  <si>
     <t>强化石</t>
   </si>
   <si>
     <t>可用于强化装备</t>
+  </si>
+  <si>
+    <t>树皮</t>
+  </si>
+  <si>
+    <t>测试木桩掉落的树皮，可以买点金币补贴家用</t>
+  </si>
+  <si>
+    <t>经验</t>
+  </si>
+  <si>
+    <t>角色经验</t>
+  </si>
+  <si>
+    <t>金币</t>
   </si>
 </sst>
 </file>
@@ -804,7 +828,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -834,6 +858,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -945,7 +972,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="黑色浅色系标题行表格样式" count="2" xr9:uid="{AD7DAD9B-8542-46E6-8BE1-BA95BA78A664}">
+    <tableStyle name="黑色浅色系标题行表格样式" count="2" xr9:uid="{A3AED00C-5B08-4615-AA51-988A4B08CA80}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -1240,66 +1267,4 @@
   </a:themeElements>
   <a:objectDefaults/>
 </a:theme>
-</file>
-
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="2"/>
-  <cols>
-    <col min="1" max="1" width="9.84166666666667" customWidth="1"/>
-    <col min="2" max="2" width="16.75" customWidth="1"/>
-    <col min="3" max="3" width="16.625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" ht="39" customHeight="1" spans="1:3">
-      <c r="A4" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="8">
-        <v>17</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/server/xlsx/道具表.xlsx
+++ b/server/xlsx/道具表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23310" windowHeight="12315" firstSheet="3"/>
+    <workbookView windowWidth="17760" windowHeight="8085" firstSheet="3"/>
   </bookViews>
   <sheets>
     <sheet name="道具表" sheetId="5" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
   <si>
     <t>id</t>
   </si>
@@ -59,22 +59,34 @@
     <t>强化石</t>
   </si>
   <si>
+    <t>⚙</t>
+  </si>
+  <si>
     <t>可用于强化装备</t>
   </si>
   <si>
     <t>树皮</t>
   </si>
   <si>
+    <t>📦</t>
+  </si>
+  <si>
     <t>测试木桩掉落的树皮，可以买点金币补贴家用</t>
   </si>
   <si>
     <t>经验</t>
   </si>
   <si>
+    <t>⏳</t>
+  </si>
+  <si>
     <t>角色经验</t>
   </si>
   <si>
     <t>金币</t>
+  </si>
+  <si>
+    <t>💰</t>
   </si>
 </sst>
 </file>
@@ -87,7 +99,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,6 +118,12 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -698,139 +716,142 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -853,7 +874,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -972,7 +993,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="黑色浅色系标题行表格样式" count="2" xr9:uid="{A3AED00C-5B08-4615-AA51-988A4B08CA80}">
+    <tableStyle name="黑色浅色系标题行表格样式" count="2" xr9:uid="{8F56FDDA-C344-43D8-B0CC-0B8FC7CF2F19}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -1267,4 +1288,120 @@
   </a:themeElements>
   <a:objectDefaults/>
 </a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="9.84166666666667" customWidth="1"/>
+    <col min="2" max="2" width="16.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" ht="39" customHeight="1" spans="1:4">
+      <c r="A4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
 </file>